--- a/placar_esteira.xlsx
+++ b/placar_esteira.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT19"/>
+  <dimension ref="A1:AT27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,17 +652,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T70_atr22_marg12</t>
+          <t>B17_zeb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤22% · sem teto</t>
+          <t>Últ.20≥90% · L≥1.5 · L≤6.5 · tot_env≥58 · atropelo≥25% · sem teto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Últ.20≥90%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -671,16 +671,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>1.75</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -691,114 +689,114 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>940</v>
+        <v>1230</v>
       </c>
       <c r="T2" t="n">
-        <v>35</v>
+        <v>207</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>28-7</t>
+          <t>124-83</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>80</v>
+        <v>59.9</v>
       </c>
       <c r="W2" t="n">
-        <v>15.97</v>
+        <v>18.87</v>
       </c>
       <c r="X2" t="n">
-        <v>45.62</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>26.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>66.53</v>
+        <v>-9.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.55</v>
+        <v>23.85</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-07-23 02:11</t>
+          <t>2026-07-20 09:10</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-01 02:46</t>
+          <t>2026-08-16 19:10</t>
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>13-2</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>4.07</v>
+        <v>9.02</v>
       </c>
       <c r="AH2" t="n">
-        <v>81.31999999999999</v>
+        <v>60.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>32-9</t>
         </is>
       </c>
       <c r="AK2" t="n">
-        <v>6.43</v>
+        <v>17.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>33.86</v>
+        <v>43.64</v>
       </c>
       <c r="AM2" t="n">
         <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>75.77</v>
+        <v>36.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.58</v>
+        <v>0.87</v>
       </c>
       <c r="AQ2" t="n">
-        <v>59.59</v>
+        <v>7.29</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.15</v>
+        <v>13.29</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="AT2" t="n">
-        <v>-44.44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T70_atr12</t>
+          <t>B01_fav</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤12% · sem teto</t>
+          <t>Todas≥55% · L≥-6.5 · L≤-2.5 · tot_env≤24 · atropelo≥31.3% · sem teto</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥55%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -807,16 +805,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -827,114 +823,114 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>933</v>
+        <v>1214</v>
       </c>
       <c r="T3" t="n">
-        <v>45</v>
+        <v>212</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>37-8</t>
+          <t>146-66</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>82.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>22.23</v>
+        <v>54.54</v>
       </c>
       <c r="X3" t="n">
-        <v>49.41</v>
+        <v>25.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.29</v>
+        <v>5.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.38</v>
+        <v>26.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>80.98999999999999</v>
+        <v>25.28</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-07-23 02:11</t>
+          <t>2026-07-20 05:51</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2026-08-05 01:21</t>
+          <t>2026-08-16 10:26</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.6</v>
+        <v>4.53</v>
       </c>
       <c r="AH3" t="n">
-        <v>80</v>
+        <v>45.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10-0</t>
+          <t>47-17</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>8.1</v>
+        <v>21.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>80.98999999999999</v>
+        <v>33.87</v>
       </c>
       <c r="AM3" t="n">
         <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.99</v>
+        <v>20.04</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.16</v>
+        <v>2.58</v>
       </c>
       <c r="AQ3" t="n">
-        <v>52.69</v>
+        <v>22.21</v>
       </c>
       <c r="AR3" t="n">
-        <v>42.14</v>
+        <v>33.87</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="AT3" t="n">
-        <v>-10.55</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T70_atr15</t>
+          <t>B02_fav</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤15% · sem teto</t>
+          <t>Todas≥55% · L≥-6.5 · L≤-1.5 · tot_env≤24 · atropelo≥31.3% · teto 5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥55%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -943,18 +939,18 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -963,114 +959,114 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>934</v>
+        <v>1215</v>
       </c>
       <c r="T4" t="n">
-        <v>128</v>
+        <v>246</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>90-38</t>
+          <t>166-80</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>70.3</v>
+        <v>67.5</v>
       </c>
       <c r="W4" t="n">
-        <v>36.07</v>
+        <v>57.73</v>
       </c>
       <c r="X4" t="n">
-        <v>28.18</v>
+        <v>23.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.9</v>
+        <v>11.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.6</v>
+        <v>5.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>31.76</v>
+        <v>18.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>22.94</v>
+        <v>25.58</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-07-23 02:11</t>
+          <t>2026-07-20 05:51</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:46</t>
+          <t>2026-08-16 10:26</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>11-4</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>3.5</v>
+        <v>5.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>31.84</v>
+        <v>34.57</v>
       </c>
       <c r="AI4" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>33-12</t>
+          <t>56-20</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>15.33</v>
+        <v>26.29</v>
       </c>
       <c r="AL4" t="n">
-        <v>34.06</v>
+        <v>34.6</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.9</v>
+        <v>8.99</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22.7</v>
+        <v>17.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>40.67</v>
+        <v>38.23</v>
       </c>
       <c r="AS4" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="AT4" t="n">
-        <v>17.97</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T70_atrmin18</t>
+          <t>B05_fav</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≥18% · sem teto</t>
+          <t>Todas≥0% · L≥-4.5 · L≤-1.5 · tot_env≤24 · atropelo≥36.49% · teto 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1079,18 +1075,18 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -1099,114 +1095,114 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>943</v>
+        <v>1218</v>
       </c>
       <c r="T5" t="n">
-        <v>524</v>
+        <v>83</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>313-211</t>
+          <t>67-16</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>59.7</v>
+        <v>80.7</v>
       </c>
       <c r="W5" t="n">
-        <v>48.47</v>
+        <v>39.46</v>
       </c>
       <c r="X5" t="n">
-        <v>9.25</v>
+        <v>47.54</v>
       </c>
       <c r="Y5" t="n">
-        <v>25.6</v>
+        <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>7.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.08</v>
+        <v>39.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.029999999999999</v>
+        <v>52.97</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-22 11:01</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2026-08-06 15:16</t>
+          <t>2026-08-11 11:04</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>38-17</t>
+          <t>13-5</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>14.44</v>
+        <v>5.96</v>
       </c>
       <c r="AH5" t="n">
-        <v>26.25</v>
+        <v>33.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>118-72</t>
+          <t>30-5</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>26.03</v>
+        <v>19.86</v>
       </c>
       <c r="AL5" t="n">
-        <v>13.7</v>
+        <v>56.73</v>
       </c>
       <c r="AM5" t="n">
         <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.22</v>
+        <v>-19.88</v>
       </c>
       <c r="AO5" t="n">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.35</v>
+        <v>4.51</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.44</v>
+        <v>48.06</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.49</v>
+        <v>46.36</v>
       </c>
       <c r="AS5" t="n">
-        <v>158</v>
+        <v>25</v>
       </c>
       <c r="AT5" t="n">
-        <v>-3.95</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bot98_original</t>
+          <t>B14_fav</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.01 · folga≥2.5 · sem teto</t>
+          <t>Todas≥55% · L≥-4.5 · L≤-1.5 · tot_env≤24 · atropelo≥31.3% · teto 5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥55%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1215,18 +1211,18 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>1.01</v>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -1235,114 +1231,114 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>926</v>
+        <v>1227</v>
       </c>
       <c r="T6" t="n">
-        <v>885</v>
+        <v>162</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>554-331</t>
+          <t>109-53</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>62.6</v>
+        <v>67.3</v>
       </c>
       <c r="W6" t="n">
-        <v>126.28</v>
+        <v>37.57</v>
       </c>
       <c r="X6" t="n">
-        <v>14.27</v>
+        <v>23.19</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.9</v>
+        <v>12.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.88</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.58</v>
+        <v>13.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.27</v>
+        <v>27.52</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-20 09:01</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-16 10:26</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>79-37</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>28.02</v>
+        <v>4.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>24.16</v>
+        <v>31.09</v>
       </c>
       <c r="AI6" t="n">
-        <v>320</v>
+        <v>56</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>202-118</t>
+          <t>43-13</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>49.17</v>
+        <v>22.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>15.36</v>
+        <v>40.4</v>
       </c>
       <c r="AM6" t="n">
         <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>11.89</v>
+        <v>3.57</v>
       </c>
       <c r="AO6" t="n">
-        <v>405</v>
+        <v>74</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.97</v>
+        <v>15.12</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.63</v>
+        <v>41.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>266</v>
+        <v>49</v>
       </c>
       <c r="AT6" t="n">
-        <v>-2.34</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T70_ctrl</t>
+          <t>B04_fav</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · sem teto</t>
+          <t>Todas≥0% · L≥-4.5 · L≤-1.5 · tot_env≤24 · atropelo≥42% · teto 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1351,18 +1347,18 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -1371,114 +1367,114 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>927</v>
+        <v>1217</v>
       </c>
       <c r="T7" t="n">
-        <v>860</v>
+        <v>111</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>538-322</t>
+          <t>87-24</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>62.6</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>123.52</v>
+        <v>48</v>
       </c>
       <c r="X7" t="n">
-        <v>14.36</v>
+        <v>43.24</v>
       </c>
       <c r="Y7" t="n">
-        <v>25.9</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.77</v>
+        <v>6.86</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.25</v>
+        <v>29.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.99</v>
+        <v>52.37</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-22 11:01</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 11:05</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76-36</t>
+          <t>17-7</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>26.83</v>
+        <v>7.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.96</v>
+        <v>30.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>196-114</t>
+          <t>41-7</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>48.75</v>
+        <v>26.96</v>
       </c>
       <c r="AL7" t="n">
-        <v>15.73</v>
+        <v>56.17</v>
       </c>
       <c r="AM7" t="n">
         <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.97</v>
+        <v>-22.27</v>
       </c>
       <c r="AO7" t="n">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.86</v>
+        <v>4.07</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.06</v>
+        <v>42.39</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.73</v>
+        <v>45.17</v>
       </c>
       <c r="AS7" t="n">
-        <v>258</v>
+        <v>34</v>
       </c>
       <c r="AT7" t="n">
-        <v>-2.33</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T70_atr32</t>
+          <t>B11_fav</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤32% · sem teto</t>
+          <t>Todas≥0% · L≥-6.5 · L≤-1.5 · tot_env≤24 · atropelo≥42% · teto 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1487,18 +1483,18 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -1507,114 +1503,114 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>939</v>
+        <v>1224</v>
       </c>
       <c r="T8" t="n">
-        <v>860</v>
+        <v>125</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>538-322</t>
+          <t>96-29</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>62.6</v>
+        <v>76.8</v>
       </c>
       <c r="W8" t="n">
-        <v>123.52</v>
+        <v>50.55</v>
       </c>
       <c r="X8" t="n">
-        <v>14.36</v>
+        <v>40.44</v>
       </c>
       <c r="Y8" t="n">
-        <v>25.9</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.77</v>
+        <v>10.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.25</v>
+        <v>25.63</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.99</v>
+        <v>45.53</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-20 11:37</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 11:01</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>76-36</t>
+          <t>24-10</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>26.83</v>
+        <v>10.13</v>
       </c>
       <c r="AH8" t="n">
-        <v>23.96</v>
+        <v>29.79</v>
       </c>
       <c r="AI8" t="n">
-        <v>310</v>
+        <v>56</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>196-114</t>
+          <t>45-11</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>48.75</v>
+        <v>26.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>15.73</v>
+        <v>47.08</v>
       </c>
       <c r="AM8" t="n">
         <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.97</v>
+        <v>-15.74</v>
       </c>
       <c r="AO8" t="n">
-        <v>397</v>
+        <v>70</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.86</v>
+        <v>4.38</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.06</v>
+        <v>44.77</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.73</v>
+        <v>30.51</v>
       </c>
       <c r="AS8" t="n">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="AT8" t="n">
-        <v>-2.33</v>
+        <v>-14.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T70_atr22_marg20</t>
+          <t>B12_fav</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤22% · sem teto</t>
+          <t>Todas≥0% · L≥-6.5 · L≤-2.5 · tot_env≤24 · atropelo≥42% · teto 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1623,18 +1619,18 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -1643,114 +1639,114 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>941</v>
+        <v>1225</v>
       </c>
       <c r="T9" t="n">
-        <v>860</v>
+        <v>124</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>538-322</t>
+          <t>96-28</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>62.6</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>123.52</v>
+        <v>51.36</v>
       </c>
       <c r="X9" t="n">
-        <v>14.36</v>
+        <v>41.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.9</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.77</v>
+        <v>12.84</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.25</v>
+        <v>31.16</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.99</v>
+        <v>44.99</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-20 11:37</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 11:01</t>
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>76-36</t>
+          <t>23-10</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>26.83</v>
+        <v>9.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>23.96</v>
+        <v>27.81</v>
       </c>
       <c r="AI9" t="n">
-        <v>310</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>196-114</t>
+          <t>44-11</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>48.75</v>
+        <v>25.41</v>
       </c>
       <c r="AL9" t="n">
-        <v>15.73</v>
+        <v>46.2</v>
       </c>
       <c r="AM9" t="n">
         <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.97</v>
+        <v>-17.18</v>
       </c>
       <c r="AO9" t="n">
-        <v>397</v>
+        <v>70</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.86</v>
+        <v>4.47</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.06</v>
+        <v>46.42</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.73</v>
+        <v>30.11</v>
       </c>
       <c r="AS9" t="n">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="AT9" t="n">
-        <v>-2.33</v>
+        <v>-16.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T70_atr28</t>
+          <t>B23_fav</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤28% · sem teto</t>
+          <t>Últ.50≥55% · L≥-6.5 · L≤-2.5 · tot_env≤24 · atropelo≥36.49% · teto 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Últ.50≥55%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1759,18 +1755,18 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -1779,114 +1775,114 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>938</v>
+        <v>1236</v>
       </c>
       <c r="T10" t="n">
-        <v>850</v>
+        <v>105</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>528-322</t>
+          <t>82-23</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>62.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>115.11</v>
+        <v>44.75</v>
       </c>
       <c r="X10" t="n">
-        <v>13.54</v>
+        <v>42.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>25.9</v>
+        <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.44</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AA10" t="n">
-        <v>13.91</v>
+        <v>46.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.99</v>
+        <v>41.74</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-22 07:49</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 11:04</t>
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>76-36</t>
+          <t>25-12</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>26.83</v>
+        <v>8.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>23.96</v>
+        <v>23.44</v>
       </c>
       <c r="AI10" t="n">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>196-114</t>
+          <t>48-12</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>48.75</v>
+        <v>27.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>15.73</v>
+        <v>45.84</v>
       </c>
       <c r="AM10" t="n">
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.97</v>
+        <v>-18.3</v>
       </c>
       <c r="AO10" t="n">
-        <v>394</v>
+        <v>47</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.68</v>
+        <v>3.68</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.24</v>
+        <v>50.12</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.91</v>
+        <v>25.53</v>
       </c>
       <c r="AS10" t="n">
-        <v>255</v>
+        <v>32</v>
       </c>
       <c r="AT10" t="n">
-        <v>-2.33</v>
+        <v>-24.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T70_atr20</t>
+          <t>B24_fav</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤20% · sem teto</t>
+          <t>Últ.20≥55% · L≥-6.5 · L≤-1.5 · tot_env≤24 · atropelo≥36.49% · teto 5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Últ.20≥55%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1895,18 +1891,18 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -1915,114 +1911,114 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>936</v>
+        <v>1237</v>
       </c>
       <c r="T11" t="n">
-        <v>521</v>
+        <v>135</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>336-185</t>
+          <t>107-28</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>64.5</v>
+        <v>79.3</v>
       </c>
       <c r="W11" t="n">
-        <v>92.88</v>
+        <v>60.9</v>
       </c>
       <c r="X11" t="n">
-        <v>17.83</v>
+        <v>45.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.2</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.72</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.56</v>
+        <v>45.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>20.06</v>
+        <v>45.06</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-07-23 00:03</t>
+          <t>2026-07-22 07:49</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 11:05</t>
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>59-28</t>
+          <t>31-16</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>20.69</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>23.79</v>
+        <v>20.51</v>
       </c>
       <c r="AI11" t="n">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>115-58</t>
+          <t>64-16</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>37.38</v>
+        <v>36.96</v>
       </c>
       <c r="AL11" t="n">
-        <v>21.61</v>
+        <v>46.2</v>
       </c>
       <c r="AM11" t="n">
         <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.73</v>
+        <v>-24.55</v>
       </c>
       <c r="AO11" t="n">
-        <v>261</v>
+        <v>47</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.04</v>
+        <v>3.77</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.91</v>
+        <v>54</v>
       </c>
       <c r="AR11" t="n">
-        <v>22.27</v>
+        <v>24.73</v>
       </c>
       <c r="AS11" t="n">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.36</v>
+        <v>-29.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T70_atr22</t>
+          <t>B16_fav</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤22% · sem teto</t>
+          <t>Últ.10≥55% · L≥-6.5 · L≤-2.5 · tot_env≤24 · atropelo≥36.49% · teto 7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Últ.10≥55%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2031,18 +2027,18 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -2051,114 +2047,114 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>928</v>
+        <v>1229</v>
       </c>
       <c r="T12" t="n">
-        <v>604</v>
+        <v>125</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>386-218</t>
+          <t>99-26</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>63.9</v>
+        <v>79.2</v>
       </c>
       <c r="W12" t="n">
-        <v>101.24</v>
+        <v>56</v>
       </c>
       <c r="X12" t="n">
-        <v>16.76</v>
+        <v>44.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.2</v>
+        <v>7</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>16.88</v>
+        <v>46.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.55</v>
+        <v>44.5</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-07-23 00:03</t>
+          <t>2026-07-22 07:49</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 11:04</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>61-30</t>
+          <t>29-15</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>20.39</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>22.41</v>
+        <v>20.4</v>
       </c>
       <c r="AI12" t="n">
-        <v>203</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>132-71</t>
+          <t>60-15</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>38.59</v>
+        <v>34.51</v>
       </c>
       <c r="AL12" t="n">
-        <v>19.01</v>
+        <v>46.02</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>5.86</v>
+        <v>-24.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>301</v>
+        <v>47</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.08</v>
+        <v>53.48</v>
       </c>
       <c r="AR12" t="n">
-        <v>20.66</v>
+        <v>24.93</v>
       </c>
       <c r="AS12" t="n">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.58</v>
+        <v>-28.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T70_atr22_minj12</t>
+          <t>B09_fav</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤22% · sem teto</t>
+          <t>Últ.10≥55% · L≥-6.5 · L≤-1.5 · tot_env≤24 · atropelo≥36.49% · sem teto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Últ.10≥55%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2167,16 +2163,14 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2187,114 +2181,114 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>942</v>
+        <v>1222</v>
       </c>
       <c r="T13" t="n">
-        <v>604</v>
+        <v>140</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>386-218</t>
+          <t>111-29</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>63.9</v>
+        <v>79.3</v>
       </c>
       <c r="W13" t="n">
-        <v>101.24</v>
+        <v>63.32</v>
       </c>
       <c r="X13" t="n">
-        <v>16.76</v>
+        <v>45.23</v>
       </c>
       <c r="Y13" t="n">
-        <v>18.2</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.55</v>
+        <v>7.91</v>
       </c>
       <c r="AA13" t="n">
-        <v>16.88</v>
+        <v>47.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.55</v>
+        <v>44.76</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-07-23 00:03</t>
+          <t>2026-07-22 07:49</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 11:05</t>
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>61-30</t>
+          <t>32-17</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>20.39</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>22.41</v>
+        <v>19.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>132-71</t>
+          <t>67-17</t>
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>38.59</v>
+        <v>38.43</v>
       </c>
       <c r="AL13" t="n">
-        <v>19.01</v>
+        <v>45.75</v>
       </c>
       <c r="AM13" t="n">
         <v>1</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.86</v>
+        <v>-25.43</v>
       </c>
       <c r="AO13" t="n">
-        <v>301</v>
+        <v>48</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.01</v>
+        <v>3.71</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.08</v>
+        <v>53.42</v>
       </c>
       <c r="AR13" t="n">
-        <v>20.66</v>
+        <v>26.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.58</v>
+        <v>-27.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T70_atr25</t>
+          <t>B21_fav</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤25% · sem teto</t>
+          <t>Últ.50≥55% · L≥-6.5 · L≤-2.5 · atropelo≥36.49% · teto 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Últ.50≥55%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2303,18 +2297,18 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -2323,114 +2317,114 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>937</v>
+        <v>1234</v>
       </c>
       <c r="T14" t="n">
-        <v>825</v>
+        <v>72</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>517-308</t>
+          <t>46-26</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>62.7</v>
+        <v>63.9</v>
       </c>
       <c r="W14" t="n">
-        <v>120.11</v>
+        <v>11.73</v>
       </c>
       <c r="X14" t="n">
-        <v>14.56</v>
+        <v>16.29</v>
       </c>
       <c r="Y14" t="n">
-        <v>25.9</v>
+        <v>4.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.64</v>
+        <v>2.41</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.95</v>
+        <v>2.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>15.53</v>
+        <v>20.29</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-22 04:45</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 10:20</t>
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>71-35</t>
+          <t>15-13</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>23.7</v>
+        <v>-0.67</v>
       </c>
       <c r="AH14" t="n">
-        <v>22.35</v>
+        <v>-2.39</v>
       </c>
       <c r="AI14" t="n">
-        <v>290</v>
+        <v>40</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>188-102</t>
+          <t>26-14</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>54.22</v>
+        <v>7.36</v>
       </c>
       <c r="AL14" t="n">
-        <v>18.7</v>
+        <v>18.41</v>
       </c>
       <c r="AM14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>6.82</v>
+        <v>-22.68</v>
       </c>
       <c r="AO14" t="n">
-        <v>385</v>
+        <v>72</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>20.07</v>
       </c>
       <c r="AR14" t="n">
-        <v>15.85</v>
+        <v>7.71</v>
       </c>
       <c r="AS14" t="n">
-        <v>248</v>
+        <v>22</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.85</v>
+        <v>-12.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T70_atr18</t>
+          <t>B07_fav</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤18% · sem teto</t>
+          <t>Todas≥0% · L≥-16.5 · L≤-12.5 · tot_env≥40 · atropelo≥42% · sem teto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2439,16 +2433,14 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-16.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2459,114 +2451,114 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>935</v>
+        <v>1220</v>
       </c>
       <c r="T15" t="n">
-        <v>336</v>
+        <v>184</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>225-111</t>
+          <t>88-96</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>67</v>
+        <v>47.8</v>
       </c>
       <c r="W15" t="n">
-        <v>75.05</v>
+        <v>-21.87</v>
       </c>
       <c r="X15" t="n">
-        <v>22.34</v>
+        <v>-11.88</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.6</v>
+        <v>40.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.45</v>
+        <v>-0.53</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.89</v>
+        <v>4.31</v>
       </c>
       <c r="AB15" t="n">
-        <v>21.41</v>
+        <v>-23.28</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-07-23 00:03</t>
+          <t>2026-07-20 05:23</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 04:46</t>
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>38-19</t>
+          <t>10-21</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>12.39</v>
+        <v>-12.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>21.74</v>
+        <v>-40.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>78-42</t>
+          <t>15-38</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>22.73</v>
+        <v>-25.27</v>
       </c>
       <c r="AL15" t="n">
-        <v>18.94</v>
+        <v>-47.68</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.33</v>
+        <v>-16.97</v>
       </c>
       <c r="AO15" t="n">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.13</v>
+        <v>-0.97</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22.74</v>
+        <v>5</v>
       </c>
       <c r="AR15" t="n">
-        <v>21.41</v>
+        <v>-50.48</v>
       </c>
       <c r="AS15" t="n">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="AT15" t="n">
-        <v>-1.33</v>
+        <v>-55.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T65_ctrl</t>
+          <t>B22_fav</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Todas≥65% · L≥5.5 · odd≥1.75 · folga≥2.5 · sem teto</t>
+          <t>Todas≥0% · L≥-12.5 · L≤-6.5 · tot_env≥40 · atropelo≥42% · teto 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Todas≥65%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2575,18 +2567,18 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-12.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -2595,114 +2587,114 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>929</v>
+        <v>1235</v>
       </c>
       <c r="T16" t="n">
-        <v>1177</v>
+        <v>133</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>712-465</t>
+          <t>65-68</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>60.5</v>
+        <v>48.9</v>
       </c>
       <c r="W16" t="n">
-        <v>124.42</v>
+        <v>-13.65</v>
       </c>
       <c r="X16" t="n">
-        <v>10.57</v>
+        <v>-10.27</v>
       </c>
       <c r="Y16" t="n">
-        <v>28.2</v>
+        <v>29.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.41</v>
+        <v>-0.47</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.98</v>
+        <v>12.16</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.92</v>
+        <v>-20.26</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-20 08:33</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 11:14</t>
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>102-52</t>
+          <t>9-28</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>32.2</v>
+        <v>-20.52</v>
       </c>
       <c r="AH16" t="n">
-        <v>20.91</v>
+        <v>-55.45</v>
       </c>
       <c r="AI16" t="n">
-        <v>420</v>
+        <v>56</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>257-163</t>
+          <t>18-38</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>50.12</v>
+        <v>-23.12</v>
       </c>
       <c r="AL16" t="n">
-        <v>11.93</v>
+        <v>-41.29</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>10.99</v>
+        <v>-35.19</v>
       </c>
       <c r="AO16" t="n">
-        <v>516</v>
+        <v>76</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.4</v>
+        <v>-0.98</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.37</v>
+        <v>10.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.03</v>
+        <v>-58.79</v>
       </c>
       <c r="AS16" t="n">
-        <v>354</v>
+        <v>40</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.66</v>
+        <v>-69.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L45_ctrl</t>
+          <t>B13_fav</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥4.5 · odd≥1.75 · folga≥2.5 · sem teto</t>
+          <t>Todas≥0% · L≥-16.5 · L≤-10.5 · tot_env≥58 · atropelo≥42% · teto 7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2711,18 +2703,18 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-16.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>7</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -2731,114 +2723,114 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>931</v>
+        <v>1226</v>
       </c>
       <c r="T17" t="n">
-        <v>1030</v>
+        <v>161</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>639-391</t>
+          <t>77-84</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>62</v>
+        <v>47.8</v>
       </c>
       <c r="W17" t="n">
-        <v>138.56</v>
+        <v>-19.17</v>
       </c>
       <c r="X17" t="n">
-        <v>13.45</v>
+        <v>-11.91</v>
       </c>
       <c r="Y17" t="n">
-        <v>27.9</v>
+        <v>38.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.96</v>
+        <v>-0.49</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.88</v>
+        <v>8.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.800000000000001</v>
+        <v>-26.82</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-07-23 00:01</t>
+          <t>2026-07-20 11:46</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-11 07:22</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>93-48</t>
+          <t>4-22</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>29.21</v>
+        <v>-18.61</v>
       </c>
       <c r="AH17" t="n">
-        <v>20.72</v>
+        <v>-71.59999999999999</v>
       </c>
       <c r="AI17" t="n">
-        <v>375</v>
+        <v>43</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>229-146</t>
+          <t>6-37</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>44.37</v>
+        <v>-31.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>11.83</v>
+        <v>-74.29000000000001</v>
       </c>
       <c r="AM17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>10.92</v>
+        <v>-44.78</v>
       </c>
       <c r="AO17" t="n">
-        <v>468</v>
+        <v>56</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.94</v>
+        <v>-0.88</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.1</v>
+        <v>13.52</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.6</v>
+        <v>-70.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>309</v>
+        <v>49</v>
       </c>
       <c r="AT17" t="n">
-        <v>-5.5</v>
+        <v>-83.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T65_atr22</t>
+          <t>B19_fav</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Todas≥65% · L≥5.5 · odd≥1.75 · folga≥2.5 · atropelo≤22% · sem teto</t>
+          <t>Todas≥0% · L≥-16.5 · L≤-12.5 · tot_env≥58 · atropelo≥42% · teto 5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Todas≥65%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2847,18 +2839,18 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-16.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>ambos</t>
@@ -2867,114 +2859,114 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>930</v>
+        <v>1232</v>
       </c>
       <c r="T18" t="n">
-        <v>790</v>
+        <v>123</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>486-304</t>
+          <t>58-65</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>61.5</v>
+        <v>47.2</v>
       </c>
       <c r="W18" t="n">
-        <v>97.65000000000001</v>
+        <v>-16.02</v>
       </c>
       <c r="X18" t="n">
-        <v>12.36</v>
+        <v>-13.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>29.6</v>
+        <v>36.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>-0.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.6</v>
+        <v>7.47</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.26</v>
+        <v>-29.59</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-07-23 00:03</t>
+          <t>2026-07-20 11:46</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2026-08-06 16:06</t>
+          <t>2026-08-10 11:58</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>79-42</t>
+          <t>4-24</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>23.23</v>
+        <v>-20.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.2</v>
+        <v>-73.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>266</v>
+        <v>32</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>164-102</t>
+          <t>4-28</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>34.03</v>
+        <v>-24.55</v>
       </c>
       <c r="AL18" t="n">
-        <v>12.79</v>
+        <v>-76.70999999999999</v>
       </c>
       <c r="AM18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>8.94</v>
+        <v>-43.79</v>
       </c>
       <c r="AO18" t="n">
-        <v>372</v>
+        <v>46</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.44</v>
+        <v>-0.86</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.56</v>
+        <v>13.64</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.24</v>
+        <v>-74.98999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.68</v>
+        <v>-88.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L45_atr22</t>
+          <t>B03_fav</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Todas≥70% · L≥4.5 · odd≥1.75 · folga≥2.5 · atropelo≤22% · sem teto</t>
+          <t>Todas≥0% · L≥-16.5 · L≤-10.5 · tot_env≥40 · atropelo≥50% · sem teto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Todas≥70%</t>
+          <t>Todas≥0%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2983,16 +2975,14 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>1.75</v>
-      </c>
+        <v>-16.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -3003,99 +2993,625 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>932</v>
+        <v>1216</v>
       </c>
       <c r="T19" t="n">
-        <v>750</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>474-276</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>116.58</v>
-      </c>
-      <c r="X19" t="n">
-        <v>15.54</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2026-07-23 00:02</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>2026-08-06 16:06</t>
-        </is>
-      </c>
-      <c r="AE19" t="n">
-        <v>117</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>76-41</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>22.08</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>261</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>162-99</t>
-        </is>
-      </c>
-      <c r="AK19" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>362</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>225</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>-2.23</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B06_fav</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Todas≥0% · L≥-4.5 · L≤-1.5 · tot_env≤24 · atropelo≥50% · teto 3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Todas≥0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>1219</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B08_fav</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Todas≥0% · L≥-6.5 · L≤-1.5 · tot_env≤24 · atropelo≥50% · teto 5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Todas≥0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>5</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>1221</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B10_fav</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Todas≥0% · L≥-4.5 · L≤-1.5 · atropelo≥50% · teto 3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Todas≥0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1223</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B15_fav</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Todas≥0% · L≥-16.5 · L≤-12.5 · tot_env≥40 · atropelo≥50% · sem teto</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Todas≥0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1228</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B18_fav</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Todas≥0% · L≥-12.5 · L≤-6.5 · tot_env≥40 · atropelo≥50% · teto 3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Todas≥0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>1231</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B20_fav</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Todas≥0% · L≥-6.5 · L≤-2.5 · tot_env≤24 · atropelo≥50% · teto 5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Todas≥0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>5</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>1233</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B25_fav</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Todas≥0% · L≥-16.5 · L≤-10.5 · tot_env≥58 · atropelo≥50% · sem teto</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Todas≥0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1238</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B26_fav</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Todas≥0% · L≥-40.5 · L≤-1.5 · tot_env≥40 · atropelo≥50% · teto 3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Todas≥0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>-40.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>1239</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3114,288 +3630,288 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>T70_atr22_marg12</t>
+          <t>B17_zeb</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>T70_atr12</t>
+          <t>B01_fav</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>T70_atr15</t>
+          <t>B02_fav</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>T70_atrmin18</t>
+          <t>B05_fav</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>bot98_original</t>
+          <t>B14_fav</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>T70_ctrl</t>
+          <t>B04_fav</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>T70_atr32</t>
+          <t>B11_fav</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>T70_atr22_marg20</t>
+          <t>B12_fav</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T70_atr22_marg12</t>
+          <t>B17_zeb</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.82</v>
+        <v>0.17</v>
       </c>
       <c r="D2" t="n">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="I2" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T70_atr12</t>
+          <t>B01_fav</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.82</v>
+        <v>0.17</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01</v>
+        <v>0.36</v>
       </c>
       <c r="F3" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="G3" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="H3" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T70_atr15</t>
+          <t>B02_fav</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01</v>
+        <v>0.38</v>
       </c>
       <c r="F4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.34</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.35</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="I4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T70_atrmin18</t>
+          <t>B05_fav</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.01</v>
+        <v>0.36</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01</v>
+        <v>0.38</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="H5" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="I5" t="n">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bot98_original</t>
+          <t>B14_fav</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="C6" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="D6" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.97</v>
+        <v>0.52</v>
       </c>
       <c r="H6" t="n">
-        <v>0.97</v>
+        <v>0.22</v>
       </c>
       <c r="I6" t="n">
-        <v>0.97</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T70_ctrl</t>
+          <t>B04_fav</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="C7" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="D7" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="E7" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="F7" t="n">
-        <v>0.97</v>
+        <v>0.52</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T70_atr32</t>
+          <t>B11_fav</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="C8" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="E8" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="F8" t="n">
-        <v>0.97</v>
+        <v>0.22</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T70_atr22_marg20</t>
+          <t>B12_fav</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="C9" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="D9" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="E9" t="n">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0.97</v>
+        <v>0.22</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
